--- a/outputs/reports/easy_ensemble_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/easy_ensemble_v1/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2562100699289994</v>
+        <v>0.1937315398738731</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08751776161818792</v>
+        <v>0.0608239348370927</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=25.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=19.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1949562418037012</v>
+        <v>0.1923046220164452</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06659431419257783</v>
+        <v>0.06037593984962403</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=19.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>대표자불일치여부</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1093935790725324</v>
+        <v>0.107103656102818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03736731026412576</v>
+        <v>0.03362625313283196</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=10.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0834101188678308</v>
+        <v>0.09740959527420803</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02849172517552673</v>
+        <v>0.03058270676691727</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=8.34%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.07228800501623002</v>
+        <v>0.0870120539634391</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02469256728518898</v>
+        <v>0.0273182957393483</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=8.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.07008575765338301</v>
+        <v>0.08407839067613988</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02394031051487805</v>
+        <v>0.02639724310776942</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=8.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.06775733986870594</v>
+        <v>0.08077552486628897</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02314495570043462</v>
+        <v>0.025360275689223</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=8.08%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.05602349063853686</v>
+        <v>0.0491338708389877</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01913683759612173</v>
+        <v>0.01542606516290718</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03345427851547132</v>
+        <v>0.03805779516244908</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01142751170177209</v>
+        <v>0.01194862155388465</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=3.35%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0253984882489458</v>
+        <v>0.02269098746707116</v>
       </c>
       <c r="F11" t="n">
-        <v>0.008675766883985359</v>
+        <v>0.007124060150375922</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=2.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/easy_ensemble_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/easy_ensemble_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1937315398738731</v>
+        <v>0.2369881283651408</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0608239348370927</v>
+        <v>0.05162945027351795</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=19.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1923046220164452</v>
+        <v>0.212956712166369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06037593984962403</v>
+        <v>0.04639404537709613</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=19.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.30%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.107103656102818</v>
+        <v>0.1194243656661127</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03362625313283196</v>
+        <v>0.02601739754282112</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=10.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09740959527420803</v>
+        <v>0.0909143299359494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03058270676691727</v>
+        <v>0.01980629539951562</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0870120539634391</v>
+        <v>0.07733439810317347</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0273182957393483</v>
+        <v>0.01684781633934174</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=8.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.08407839067613988</v>
+        <v>0.05831261422949655</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02639724310776942</v>
+        <v>0.01270379338175942</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=8.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.08077552486628897</v>
+        <v>0.04704197059259392</v>
       </c>
       <c r="F8" t="n">
-        <v>0.025360275689223</v>
+        <v>0.01024840821450984</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=8.08%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0491338708389877</v>
+        <v>0.04169891162959222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01542606516290718</v>
+        <v>0.009084387050488751</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.17%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03805779516244908</v>
+        <v>0.03488218925460607</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01194862155388465</v>
+        <v>0.007599318446775971</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02269098746707116</v>
+        <v>0.03102925921657064</v>
       </c>
       <c r="F11" t="n">
-        <v>0.007124060150375922</v>
+        <v>0.006759931844677491</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/easy_ensemble_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/easy_ensemble_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2369881283651408</v>
+        <v>0.2936518688692807</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05162945027351795</v>
+        <v>0.07443643303687553</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=29.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.212956712166369</v>
+        <v>0.2751346848417932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04639404537709613</v>
+        <v>0.06974259902791458</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.30%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=27.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1194243656661127</v>
+        <v>0.07662839666667617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02601739754282112</v>
+        <v>0.01942417236834032</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=7.66%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0909143299359494</v>
+        <v>0.06540393922535705</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01980629539951562</v>
+        <v>0.01657893736975791</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.07733439810317347</v>
+        <v>0.06234848856079634</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01684781633934174</v>
+        <v>0.01580442553141748</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05831261422949655</v>
+        <v>0.05386240671507315</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01270379338175942</v>
+        <v>0.0136533285011588</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=5.39%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04704197059259392</v>
+        <v>0.02828309615157349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01024840821450984</v>
+        <v>0.007169349205467801</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>누적자부담집행금액</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04169891162959222</v>
+        <v>0.02717621591082704</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009084387050488751</v>
+        <v>0.006888771331955812</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.17%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 누적자부담집행금액(CUMU_PYHWY_EXE_AMT). 기여도(정규화 비중)=2.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03488218925460607</v>
+        <v>0.02492786542181072</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007599318446775971</v>
+        <v>0.006318847526384563</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03102925921657064</v>
+        <v>0.01588834345571474</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006759931844677491</v>
+        <v>0.004027461559370005</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=1.59%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
